--- a/experiments/results/abp/cplex-cp.xlsx
+++ b/experiments/results/abp/cplex-cp.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>323.3</t>
+          <t>312.4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>208.7</t>
+          <t>208.3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.01</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>132.4</t>
+          <t>138.1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1389,17 +1389,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>183</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>195.1</t>
+          <t>162.6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>126.1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>187.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>141.9</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>755.27</t>
+          <t>281.02</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1682,22 +1682,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>110.3</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>211.1</t>
+          <t>205.6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>206.7</t>
+          <t>204.2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1923,17 +1923,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>239.4</t>
+          <t>232.8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>183.23</t>
+          <t>198.98</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>188.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>128.9</t>
+          <t>143.6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>117.35</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>152.9</t>
+          <t>188.8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.05</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2851,17 +2851,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>188.9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2904,22 +2904,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>180.6</t>
+          <t>211.7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2962,22 +2962,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>165.8</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>112.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>133.20</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>206.2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>183.2</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3198,22 +3198,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>394</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>219.3</t>
+          <t>234.4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.08</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>144.6</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>67.94</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>240.3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.10</t>
+          <t>1800.11</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>258.4</t>
+          <t>251.9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.11</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3439,17 +3439,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>276.4</t>
+          <t>285.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.13</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3558,35 +3558,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>569.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3616,32 +3620,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>74.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3678,35 +3682,39 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>637.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3736,35 +3744,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>412.7</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3794,35 +3806,39 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>476.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3852,32 +3868,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3914,35 +3930,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>409.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3972,35 +3992,39 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>916.02</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4030,35 +4054,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>546.7</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4088,35 +4116,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>281.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4146,35 +4178,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>180.4</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4204,12 +4240,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4224,12 +4260,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4266,32 +4302,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>240.1</t>
+          <t>144.4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -4324,32 +4360,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>239.6</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -4382,35 +4418,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>361</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4440,32 +4480,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>330.0</t>
+          <t>175.9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -4498,35 +4538,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>455</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>319.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4556,27 +4600,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>302.8</t>
+          <t>310.3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4614,35 +4658,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>262</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>279.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4672,35 +4720,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>340</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>402.4</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>16.11</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4730,32 +4782,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>193.1</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4792,35 +4844,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>385.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4850,32 +4906,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>454.6</t>
+          <t>245.6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -4908,32 +4964,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>224</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>581</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>476.3</t>
+          <t>238.8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.05</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -5042,35 +5098,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>436.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5100,32 +5160,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -5162,32 +5222,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -5224,32 +5284,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -5286,32 +5346,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5348,32 +5408,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -5410,32 +5470,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>145.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -5472,32 +5532,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>333.4</t>
+          <t>377.7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -5530,35 +5590,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>542.9</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5588,35 +5652,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>299.8</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5646,35 +5714,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>127</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5704,12 +5776,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5724,12 +5796,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5766,32 +5838,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>233.4</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -5824,32 +5896,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>235.8</t>
+          <t>171.9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -5882,35 +5954,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>451</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>451</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>429.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5940,32 +6016,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>308.1</t>
+          <t>210.2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -5998,35 +6074,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>567</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6056,32 +6136,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>312.9</t>
+          <t>262.7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -6114,35 +6194,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>327</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>265.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6172,35 +6256,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>424</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>411.1</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>4.54</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6230,32 +6318,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>826</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>826</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>191.7</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>79.05</t>
+          <t>59.48</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6292,35 +6380,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>412</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>386.4</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6350,17 +6442,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>310</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6370,12 +6462,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>387.1</t>
+          <t>249.3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -6408,32 +6500,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>245</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>726</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>410.3</t>
+          <t>278.1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -6542,35 +6634,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>402.4</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6600,32 +6696,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -6662,32 +6758,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -6724,32 +6820,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -6786,32 +6882,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -6848,32 +6944,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -6910,32 +7006,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>242.45</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -6972,12 +7068,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6987,17 +7083,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>379.6</t>
+          <t>499.7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -7030,35 +7126,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>605.6</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7088,35 +7188,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>285.4</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7146,35 +7250,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>153</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>136.6</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7204,12 +7312,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -7224,12 +7332,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7266,32 +7374,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.05</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -7324,32 +7432,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>271.7</t>
+          <t>172.6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -7382,35 +7490,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>541</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>548.9</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7440,32 +7552,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>271</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>437.1</t>
+          <t>267.6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -7498,35 +7610,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>681</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>224.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7556,12 +7672,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7571,17 +7687,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>331.4</t>
+          <t>318.1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -7614,35 +7730,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>392</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7672,35 +7792,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>508</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>508</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>443.3</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7730,32 +7854,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>331</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>991</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>991</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>251.2</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>197.93</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -7792,35 +7916,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>494</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>419.7</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7850,17 +7978,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>476</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -7870,7 +7998,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>449.7</t>
+          <t>307.6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -7908,32 +8036,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>451.4</t>
+          <t>280.7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.05</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
